--- a/diseases/d116/2010-2014.xlsx
+++ b/diseases/d116/2010-2014.xlsx
@@ -8706,7 +8706,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -15222,7 +15222,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -16322,7 +16322,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -17126,7 +17126,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -18226,7 +18226,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -19030,7 +19030,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -20786,7 +20786,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -21188,7 +21188,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -21590,7 +21590,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -22288,7 +22288,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -22690,7 +22690,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -23092,7 +23092,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -23494,7 +23494,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -24192,7 +24192,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -24594,7 +24594,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -24996,7 +24996,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -25398,7 +25398,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -25948,7 +25948,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26350,7 +26350,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -26752,7 +26752,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -27154,7 +27154,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -27556,7 +27556,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -28106,7 +28106,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -28508,7 +28508,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -28910,7 +28910,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -29312,7 +29312,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -30010,7 +30010,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -30412,7 +30412,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -31216,7 +31216,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -31618,7 +31618,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -32316,7 +32316,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -32718,7 +32718,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -33120,7 +33120,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -33522,7 +33522,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -34220,7 +34220,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
@@ -34622,7 +34622,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -35024,7 +35024,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -35426,7 +35426,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -35976,7 +35976,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -36378,7 +36378,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -36780,7 +36780,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -37182,7 +37182,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -37584,7 +37584,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -38282,7 +38282,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -38684,7 +38684,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -39086,7 +39086,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -39488,7 +39488,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -40186,7 +40186,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -40588,7 +40588,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -40990,7 +40990,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -41392,7 +41392,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -42090,7 +42090,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -42492,7 +42492,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -42894,7 +42894,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -43296,7 +43296,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -43994,7 +43994,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -44396,7 +44396,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -44798,7 +44798,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -45200,7 +45200,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -45602,7 +45602,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -46152,7 +46152,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -46554,7 +46554,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -46956,7 +46956,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -47358,7 +47358,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -48056,7 +48056,7 @@
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">
@@ -48458,7 +48458,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -48860,7 +48860,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -49262,7 +49262,7 @@
       </c>
       <c r="AJ266" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK266" t="inlineStr">
@@ -49664,7 +49664,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -50362,7 +50362,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -50764,7 +50764,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -51166,7 +51166,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -51568,7 +51568,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -52266,7 +52266,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -52668,7 +52668,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">
@@ -53070,7 +53070,7 @@
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -53472,7 +53472,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -54170,7 +54170,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -54572,7 +54572,7 @@
       </c>
       <c r="AJ294" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr">
@@ -54974,7 +54974,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -55376,7 +55376,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -55778,7 +55778,7 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
@@ -56476,7 +56476,7 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -56878,7 +56878,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -57280,7 +57280,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -57682,7 +57682,7 @@
       </c>
       <c r="AJ310" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK310" t="inlineStr">
@@ -58380,7 +58380,7 @@
       </c>
       <c r="AJ314" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK314" t="inlineStr">
@@ -58782,7 +58782,7 @@
       </c>
       <c r="AJ316" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK316" t="inlineStr">
@@ -59184,7 +59184,7 @@
       </c>
       <c r="AJ318" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK318" t="inlineStr">
@@ -59586,7 +59586,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -60284,7 +60284,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -60686,7 +60686,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -61088,7 +61088,7 @@
       </c>
       <c r="AJ328" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK328" t="inlineStr">
@@ -61490,7 +61490,7 @@
       </c>
       <c r="AJ330" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK330" t="inlineStr">
@@ -61892,7 +61892,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -62590,7 +62590,7 @@
       </c>
       <c r="AJ336" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK336" t="inlineStr">
@@ -62992,7 +62992,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -63394,7 +63394,7 @@
       </c>
       <c r="AJ340" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK340" t="inlineStr">
@@ -63796,7 +63796,7 @@
       </c>
       <c r="AJ342" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK342" t="inlineStr">

--- a/diseases/d116/2010-2014.xlsx
+++ b/diseases/d116/2010-2014.xlsx
@@ -8706,7 +8706,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -15222,7 +15222,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -16322,7 +16322,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -17126,7 +17126,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -18226,7 +18226,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -19030,7 +19030,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -20786,7 +20786,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -21188,7 +21188,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -21590,7 +21590,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -22288,7 +22288,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -22690,7 +22690,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -23092,7 +23092,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -23494,7 +23494,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -24192,7 +24192,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -24594,7 +24594,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -24996,7 +24996,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -25398,7 +25398,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -25948,7 +25948,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26350,7 +26350,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -26752,7 +26752,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -27154,7 +27154,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -27556,7 +27556,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -28106,7 +28106,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -28508,7 +28508,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -28910,7 +28910,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -29312,7 +29312,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -30010,7 +30010,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -30412,7 +30412,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -31216,7 +31216,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -31618,7 +31618,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -32316,7 +32316,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -32718,7 +32718,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -33120,7 +33120,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -33522,7 +33522,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -34220,7 +34220,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
@@ -34622,7 +34622,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -35024,7 +35024,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -35426,7 +35426,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -35976,7 +35976,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -36378,7 +36378,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -36780,7 +36780,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -37182,7 +37182,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -37584,7 +37584,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -38282,7 +38282,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -38684,7 +38684,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -39086,7 +39086,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -39488,7 +39488,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -40186,7 +40186,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -40588,7 +40588,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -40990,7 +40990,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -41392,7 +41392,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -42090,7 +42090,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -42492,7 +42492,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -42894,7 +42894,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -43296,7 +43296,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -43994,7 +43994,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -44396,7 +44396,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -44798,7 +44798,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -45200,7 +45200,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -45602,7 +45602,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -46152,7 +46152,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -46554,7 +46554,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -46956,7 +46956,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -47358,7 +47358,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -48056,7 +48056,7 @@
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">
@@ -48458,7 +48458,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -48860,7 +48860,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -49262,7 +49262,7 @@
       </c>
       <c r="AJ266" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK266" t="inlineStr">
@@ -49664,7 +49664,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -50362,7 +50362,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -50764,7 +50764,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -51166,7 +51166,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -51568,7 +51568,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -52266,7 +52266,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -52668,7 +52668,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">
@@ -53070,7 +53070,7 @@
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -53472,7 +53472,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -54170,7 +54170,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -54572,7 +54572,7 @@
       </c>
       <c r="AJ294" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr">
@@ -54974,7 +54974,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -55376,7 +55376,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -55778,7 +55778,7 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
@@ -56476,7 +56476,7 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -56878,7 +56878,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -57280,7 +57280,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -57682,7 +57682,7 @@
       </c>
       <c r="AJ310" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK310" t="inlineStr">
@@ -58380,7 +58380,7 @@
       </c>
       <c r="AJ314" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK314" t="inlineStr">
@@ -58782,7 +58782,7 @@
       </c>
       <c r="AJ316" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK316" t="inlineStr">
@@ -59184,7 +59184,7 @@
       </c>
       <c r="AJ318" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK318" t="inlineStr">
@@ -59586,7 +59586,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -60284,7 +60284,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -60686,7 +60686,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -61088,7 +61088,7 @@
       </c>
       <c r="AJ328" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK328" t="inlineStr">
@@ -61490,7 +61490,7 @@
       </c>
       <c r="AJ330" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK330" t="inlineStr">
@@ -61892,7 +61892,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -62590,7 +62590,7 @@
       </c>
       <c r="AJ336" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK336" t="inlineStr">
@@ -62992,7 +62992,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -63394,7 +63394,7 @@
       </c>
       <c r="AJ340" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK340" t="inlineStr">
@@ -63796,7 +63796,7 @@
       </c>
       <c r="AJ342" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK342" t="inlineStr">

--- a/diseases/d116/2010-2014.xlsx
+++ b/diseases/d116/2010-2014.xlsx
@@ -2541,9 +2541,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -2837,9 +2834,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3133,9 +3127,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -3429,9 +3420,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -3725,9 +3713,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -3873,9 +3858,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4169,9 +4151,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4465,9 +4444,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -4761,9 +4737,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -5057,9 +5030,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5353,9 +5323,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5649,9 +5616,6 @@
       <c r="O35" t="n">
         <v>1</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -5797,9 +5761,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -6093,9 +6054,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -6389,9 +6347,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -6685,9 +6640,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -6981,9 +6933,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -7277,9 +7226,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -7573,9 +7519,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -7869,9 +7812,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -8165,9 +8105,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -8464,9 +8401,6 @@
       <c r="P54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -8716,7 +8650,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -8866,9 +8800,6 @@
       <c r="P56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -9118,7 +9049,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -9268,9 +9199,6 @@
       <c r="P58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -9520,7 +9448,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -9667,9 +9595,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -9966,9 +9891,6 @@
       <c r="P62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -10218,7 +10140,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -10368,9 +10290,6 @@
       <c r="P64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -10620,7 +10539,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -10770,9 +10689,6 @@
       <c r="P66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -11022,7 +10938,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -11172,9 +11088,6 @@
       <c r="P68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -11424,7 +11337,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -11571,9 +11484,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -11870,9 +11780,6 @@
       <c r="P72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -12122,7 +12029,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -12272,9 +12179,6 @@
       <c r="P74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -12524,7 +12428,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -12674,9 +12578,6 @@
       <c r="P76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -12926,7 +12827,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -13076,9 +12977,6 @@
       <c r="P78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -13328,7 +13226,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -13475,9 +13373,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -13774,9 +13669,6 @@
       <c r="P82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -14026,7 +13918,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -14176,9 +14068,6 @@
       <c r="P84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -14428,7 +14317,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -14578,9 +14467,6 @@
       <c r="P86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -14830,7 +14716,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -14980,9 +14866,6 @@
       <c r="P88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -15232,7 +15115,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -15382,9 +15265,6 @@
       <c r="P90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -15634,7 +15514,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -15781,9 +15661,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -16080,9 +15957,6 @@
       <c r="P94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -16332,7 +16206,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -16482,9 +16356,6 @@
       <c r="P96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -16734,7 +16605,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -16884,9 +16755,6 @@
       <c r="P98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -17136,7 +17004,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -17286,9 +17154,6 @@
       <c r="P100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -17538,7 +17403,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -17685,9 +17550,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -17984,9 +17846,6 @@
       <c r="P104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -18236,7 +18095,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -18386,9 +18245,6 @@
       <c r="P106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -18638,7 +18494,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -18788,9 +18644,6 @@
       <c r="P108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -19040,7 +18893,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -19190,9 +19043,6 @@
       <c r="P110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -19442,7 +19292,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -19589,9 +19439,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -19740,9 +19587,6 @@
       <c r="P113" t="n">
         <v>2</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.001565880767159907</v>
       </c>
@@ -19992,7 +19836,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -20142,9 +19986,6 @@
       <c r="P115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -20394,7 +20235,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -20544,9 +20385,6 @@
       <c r="P117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -20796,7 +20634,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -20946,9 +20784,6 @@
       <c r="P119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -21198,7 +21033,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -21348,9 +21183,6 @@
       <c r="P121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -21600,7 +21432,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -21747,9 +21579,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -22046,9 +21875,6 @@
       <c r="P125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -22298,7 +22124,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -22448,9 +22274,6 @@
       <c r="P127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -22700,7 +22523,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -22850,9 +22673,6 @@
       <c r="P129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -23102,7 +22922,7 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN130" t="b">
@@ -23252,9 +23072,6 @@
       <c r="P131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -23504,7 +23321,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -23651,9 +23468,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -23950,9 +23764,6 @@
       <c r="P135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -24202,7 +24013,7 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN136" t="b">
@@ -24352,9 +24163,6 @@
       <c r="P137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -24604,7 +24412,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -24754,9 +24562,6 @@
       <c r="P139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -25006,7 +24811,7 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -25156,9 +24961,6 @@
       <c r="P141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -25408,7 +25210,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -25555,9 +25357,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -25706,9 +25505,6 @@
       <c r="P144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -25958,7 +25754,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -26108,9 +25904,6 @@
       <c r="P146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -26360,7 +26153,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -26510,9 +26303,6 @@
       <c r="P148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -26762,7 +26552,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -26912,9 +26702,6 @@
       <c r="P150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -27164,7 +26951,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -27314,9 +27101,6 @@
       <c r="P152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -27566,7 +27350,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -27713,9 +27497,6 @@
       <c r="O154" t="n">
         <v>2</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -27864,9 +27645,6 @@
       <c r="P155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -28116,7 +27894,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -28266,9 +28044,6 @@
       <c r="P157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
@@ -28518,7 +28293,7 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -28668,9 +28443,6 @@
       <c r="P159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
@@ -28920,7 +28692,7 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN160" t="b">
@@ -29070,9 +28842,6 @@
       <c r="P161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -29322,7 +29091,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -29469,9 +29238,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -29768,9 +29534,6 @@
       <c r="P165" t="n">
         <v>0</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
@@ -30020,7 +29783,7 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN166" t="b">
@@ -30170,9 +29933,6 @@
       <c r="P167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -30422,7 +30182,7 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN168" t="b">
@@ -30572,9 +30332,6 @@
       <c r="P169" t="n">
         <v>0</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
@@ -30824,7 +30581,7 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN170" t="b">
@@ -30974,9 +30731,6 @@
       <c r="P171" t="n">
         <v>0</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
@@ -31226,7 +30980,7 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN172" t="b">
@@ -31376,9 +31130,6 @@
       <c r="P173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -31628,7 +31379,7 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN174" t="b">
@@ -31775,9 +31526,6 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0</v>
       </c>
@@ -32074,9 +31822,6 @@
       <c r="P177" t="n">
         <v>0</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0</v>
       </c>
@@ -32326,7 +32071,7 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN178" t="b">
@@ -32476,9 +32221,6 @@
       <c r="P179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -32728,7 +32470,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -32878,9 +32620,6 @@
       <c r="P181" t="n">
         <v>0</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0</v>
       </c>
@@ -33130,7 +32869,7 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN182" t="b">
@@ -33280,9 +33019,6 @@
       <c r="P183" t="n">
         <v>0</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
@@ -33532,7 +33268,7 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN184" t="b">
@@ -33679,9 +33415,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -33978,9 +33711,6 @@
       <c r="P187" t="n">
         <v>1</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.0007829403835799535</v>
       </c>
@@ -34230,7 +33960,7 @@
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN188" t="b">
@@ -34380,9 +34110,6 @@
       <c r="P189" t="n">
         <v>1</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.0007829403835799535</v>
       </c>
@@ -34632,7 +34359,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -34782,9 +34509,6 @@
       <c r="P191" t="n">
         <v>0</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0</v>
       </c>
@@ -35034,7 +34758,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -35184,9 +34908,6 @@
       <c r="P193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -35436,7 +35157,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -35583,9 +35304,6 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0</v>
       </c>
@@ -35734,9 +35452,6 @@
       <c r="P196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -35986,7 +35701,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -36136,9 +35851,6 @@
       <c r="P198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -36388,7 +36100,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -36538,9 +36250,6 @@
       <c r="P200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -36790,7 +36499,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -36940,9 +36649,6 @@
       <c r="P202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -37192,7 +36898,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -37342,9 +37048,6 @@
       <c r="P204" t="n">
         <v>0</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0</v>
       </c>
@@ -37594,7 +37297,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -37741,9 +37444,6 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0</v>
       </c>
@@ -38040,9 +37740,6 @@
       <c r="P208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -38292,7 +37989,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -38442,9 +38139,6 @@
       <c r="P210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -38694,7 +38388,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -38844,9 +38538,6 @@
       <c r="P212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -39096,7 +38787,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -39246,9 +38937,6 @@
       <c r="P214" t="n">
         <v>0</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0</v>
       </c>
@@ -39498,7 +39186,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -39645,9 +39333,6 @@
       <c r="O216" t="n">
         <v>0</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0</v>
       </c>
@@ -39944,9 +39629,6 @@
       <c r="P218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -40196,7 +39878,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -40346,9 +40028,6 @@
       <c r="P220" t="n">
         <v>0</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
@@ -40598,7 +40277,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -40748,9 +40427,6 @@
       <c r="P222" t="n">
         <v>0</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0</v>
       </c>
@@ -41000,7 +40676,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -41150,9 +40826,6 @@
       <c r="P224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -41402,7 +41075,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -41549,9 +41222,6 @@
       <c r="O226" t="n">
         <v>0</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0</v>
       </c>
@@ -41848,9 +41518,6 @@
       <c r="P228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -42100,7 +41767,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -42250,9 +41917,6 @@
       <c r="P230" t="n">
         <v>0</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0</v>
       </c>
@@ -42502,7 +42166,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -42652,9 +42316,6 @@
       <c r="P232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
@@ -42904,7 +42565,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -43054,9 +42715,6 @@
       <c r="P234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
@@ -43306,7 +42964,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -43453,9 +43111,6 @@
       <c r="O236" t="n">
         <v>0</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0</v>
       </c>
@@ -43752,9 +43407,6 @@
       <c r="P238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
@@ -44004,7 +43656,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -44154,9 +43806,6 @@
       <c r="P240" t="n">
         <v>0</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
@@ -44406,7 +44055,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -44556,9 +44205,6 @@
       <c r="P242" t="n">
         <v>0</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0</v>
       </c>
@@ -44808,7 +44454,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -44958,9 +44604,6 @@
       <c r="P244" t="n">
         <v>0</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0</v>
       </c>
@@ -45210,7 +44853,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -45360,9 +45003,6 @@
       <c r="P246" t="n">
         <v>0</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0</v>
       </c>
@@ -45612,7 +45252,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -45759,9 +45399,6 @@
       <c r="O248" t="n">
         <v>1</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -45910,9 +45547,6 @@
       <c r="P249" t="n">
         <v>0</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0</v>
       </c>
@@ -46162,7 +45796,7 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN250" t="b">
@@ -46312,9 +45946,6 @@
       <c r="P251" t="n">
         <v>0</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0</v>
       </c>
@@ -46564,7 +46195,7 @@
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN252" t="b">
@@ -46714,9 +46345,6 @@
       <c r="P253" t="n">
         <v>0</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>0</v>
       </c>
@@ -46966,7 +46594,7 @@
       </c>
       <c r="AM254" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN254" t="b">
@@ -47116,9 +46744,6 @@
       <c r="P255" t="n">
         <v>0</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0</v>
       </c>
@@ -47368,7 +46993,7 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN256" t="b">
@@ -47515,9 +47140,6 @@
       <c r="O257" t="n">
         <v>0</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0</v>
       </c>
@@ -47814,9 +47436,6 @@
       <c r="P259" t="n">
         <v>0</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0</v>
       </c>
@@ -48066,7 +47685,7 @@
       </c>
       <c r="AM260" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN260" t="b">
@@ -48216,9 +47835,6 @@
       <c r="P261" t="n">
         <v>0</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0</v>
       </c>
@@ -48468,7 +48084,7 @@
       </c>
       <c r="AM262" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN262" t="b">
@@ -48618,9 +48234,6 @@
       <c r="P263" t="n">
         <v>0</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0</v>
       </c>
@@ -48870,7 +48483,7 @@
       </c>
       <c r="AM264" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN264" t="b">
@@ -49020,9 +48633,6 @@
       <c r="P265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
@@ -49272,7 +48882,7 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN266" t="b">
@@ -49422,9 +49032,6 @@
       <c r="P267" t="n">
         <v>0</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0</v>
       </c>
@@ -49674,7 +49281,7 @@
       </c>
       <c r="AM268" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN268" t="b">
@@ -49821,9 +49428,6 @@
       <c r="O269" t="n">
         <v>0</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0</v>
       </c>
@@ -50120,9 +49724,6 @@
       <c r="P271" t="n">
         <v>0</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0</v>
       </c>
@@ -50372,7 +49973,7 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN272" t="b">
@@ -50522,9 +50123,6 @@
       <c r="P273" t="n">
         <v>0</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0</v>
       </c>
@@ -50774,7 +50372,7 @@
       </c>
       <c r="AM274" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN274" t="b">
@@ -50924,9 +50522,6 @@
       <c r="P275" t="n">
         <v>0</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0</v>
       </c>
@@ -51176,7 +50771,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -51326,9 +50921,6 @@
       <c r="P277" t="n">
         <v>0</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0</v>
       </c>
@@ -51578,7 +51170,7 @@
       </c>
       <c r="AM278" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN278" t="b">
@@ -51725,9 +51317,6 @@
       <c r="O279" t="n">
         <v>0</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0</v>
       </c>
@@ -52024,9 +51613,6 @@
       <c r="P281" t="n">
         <v>0</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0</v>
       </c>
@@ -52276,7 +51862,7 @@
       </c>
       <c r="AM282" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN282" t="b">
@@ -52426,9 +52012,6 @@
       <c r="P283" t="n">
         <v>0</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0</v>
       </c>
@@ -52678,7 +52261,7 @@
       </c>
       <c r="AM284" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN284" t="b">
@@ -52828,9 +52411,6 @@
       <c r="P285" t="n">
         <v>0</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0</v>
       </c>
@@ -53080,7 +52660,7 @@
       </c>
       <c r="AM286" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN286" t="b">
@@ -53230,9 +52810,6 @@
       <c r="P287" t="n">
         <v>0</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0</v>
       </c>
@@ -53482,7 +53059,7 @@
       </c>
       <c r="AM288" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN288" t="b">
@@ -53629,9 +53206,6 @@
       <c r="O289" t="n">
         <v>0</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>0</v>
       </c>
@@ -53928,9 +53502,6 @@
       <c r="P291" t="n">
         <v>0</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>0</v>
       </c>
@@ -54180,7 +53751,7 @@
       </c>
       <c r="AM292" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN292" t="b">
@@ -54330,9 +53901,6 @@
       <c r="P293" t="n">
         <v>0</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0</v>
       </c>
@@ -54582,7 +54150,7 @@
       </c>
       <c r="AM294" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN294" t="b">
@@ -54732,9 +54300,6 @@
       <c r="P295" t="n">
         <v>0</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0</v>
       </c>
@@ -54984,7 +54549,7 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN296" t="b">
@@ -55134,9 +54699,6 @@
       <c r="P297" t="n">
         <v>0</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0</v>
       </c>
@@ -55386,7 +54948,7 @@
       </c>
       <c r="AM298" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN298" t="b">
@@ -55536,9 +55098,6 @@
       <c r="P299" t="n">
         <v>0</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0</v>
       </c>
@@ -55788,7 +55347,7 @@
       </c>
       <c r="AM300" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN300" t="b">
@@ -55935,9 +55494,6 @@
       <c r="O301" t="n">
         <v>0</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0</v>
       </c>
@@ -56234,9 +55790,6 @@
       <c r="P303" t="n">
         <v>0</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0</v>
       </c>
@@ -56486,7 +56039,7 @@
       </c>
       <c r="AM304" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN304" t="b">
@@ -56636,9 +56189,6 @@
       <c r="P305" t="n">
         <v>0</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0</v>
       </c>
@@ -56888,7 +56438,7 @@
       </c>
       <c r="AM306" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN306" t="b">
@@ -57038,9 +56588,6 @@
       <c r="P307" t="n">
         <v>0</v>
       </c>
-      <c r="Q307" t="n">
-        <v>0</v>
-      </c>
       <c r="R307" t="n">
         <v>0</v>
       </c>
@@ -57290,7 +56837,7 @@
       </c>
       <c r="AM308" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN308" t="b">
@@ -57440,9 +56987,6 @@
       <c r="P309" t="n">
         <v>0</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0</v>
       </c>
@@ -57692,7 +57236,7 @@
       </c>
       <c r="AM310" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN310" t="b">
@@ -57839,9 +57383,6 @@
       <c r="O311" t="n">
         <v>1</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -58138,9 +57679,6 @@
       <c r="P313" t="n">
         <v>0</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0</v>
       </c>
@@ -58390,7 +57928,7 @@
       </c>
       <c r="AM314" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN314" t="b">
@@ -58540,9 +58078,6 @@
       <c r="P315" t="n">
         <v>0</v>
       </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
       <c r="R315" t="n">
         <v>0</v>
       </c>
@@ -58792,7 +58327,7 @@
       </c>
       <c r="AM316" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN316" t="b">
@@ -58942,9 +58477,6 @@
       <c r="P317" t="n">
         <v>0</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0</v>
       </c>
@@ -59194,7 +58726,7 @@
       </c>
       <c r="AM318" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN318" t="b">
@@ -59344,9 +58876,6 @@
       <c r="P319" t="n">
         <v>0</v>
       </c>
-      <c r="Q319" t="n">
-        <v>0</v>
-      </c>
       <c r="R319" t="n">
         <v>0</v>
       </c>
@@ -59596,7 +59125,7 @@
       </c>
       <c r="AM320" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN320" t="b">
@@ -59743,9 +59272,6 @@
       <c r="O321" t="n">
         <v>0</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0</v>
       </c>
@@ -60042,9 +59568,6 @@
       <c r="P323" t="n">
         <v>0</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>0</v>
       </c>
@@ -60294,7 +59817,7 @@
       </c>
       <c r="AM324" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN324" t="b">
@@ -60444,9 +59967,6 @@
       <c r="P325" t="n">
         <v>0</v>
       </c>
-      <c r="Q325" t="n">
-        <v>0</v>
-      </c>
       <c r="R325" t="n">
         <v>0</v>
       </c>
@@ -60696,7 +60216,7 @@
       </c>
       <c r="AM326" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN326" t="b">
@@ -60846,9 +60366,6 @@
       <c r="P327" t="n">
         <v>0</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0</v>
       </c>
@@ -61098,7 +60615,7 @@
       </c>
       <c r="AM328" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN328" t="b">
@@ -61248,9 +60765,6 @@
       <c r="P329" t="n">
         <v>0</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0</v>
       </c>
@@ -61500,7 +61014,7 @@
       </c>
       <c r="AM330" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN330" t="b">
@@ -61650,9 +61164,6 @@
       <c r="P331" t="n">
         <v>0</v>
       </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
       <c r="R331" t="n">
         <v>0</v>
       </c>
@@ -61902,7 +61413,7 @@
       </c>
       <c r="AM332" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN332" t="b">
@@ -62049,9 +61560,6 @@
       <c r="O333" t="n">
         <v>0</v>
       </c>
-      <c r="Q333" t="n">
-        <v>0</v>
-      </c>
       <c r="R333" t="n">
         <v>0</v>
       </c>
@@ -62348,9 +61856,6 @@
       <c r="P335" t="n">
         <v>0</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>0</v>
       </c>
@@ -62600,7 +62105,7 @@
       </c>
       <c r="AM336" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN336" t="b">
@@ -62750,9 +62255,6 @@
       <c r="P337" t="n">
         <v>0</v>
       </c>
-      <c r="Q337" t="n">
-        <v>0</v>
-      </c>
       <c r="R337" t="n">
         <v>0</v>
       </c>
@@ -63002,7 +62504,7 @@
       </c>
       <c r="AM338" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN338" t="b">
@@ -63152,9 +62654,6 @@
       <c r="P339" t="n">
         <v>0</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0</v>
       </c>
@@ -63404,7 +62903,7 @@
       </c>
       <c r="AM340" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN340" t="b">
@@ -63554,9 +63053,6 @@
       <c r="P341" t="n">
         <v>0</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0</v>
       </c>
@@ -63806,7 +63302,7 @@
       </c>
       <c r="AM342" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN342" t="b">
